--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/hygiene/Betriebsklar-Nachpruefliste-Lebensmittelhygiene.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/hygiene/Betriebsklar-Nachpruefliste-Lebensmittelhygiene.xlsx
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: Inhalt seit Ihrer Freigabe geändert und/oder ohne unterschriebenes Blatt. Die Prüfsumme bestimmt die Fassung; jede Änderung ergibt eine neue.</t>
+          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu den Vorlagen liegen die aktuellen PDFs bei.</t>
+          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0c1fcf56415c</t>
+          <t>58d605e11929</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung d865b088727e (bisherige Rechnung bf971591cc3e), heute 0c1fcf56415c. Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>a9706524831a</t>
+          <t>95846129d507</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung efa3132a1835 (bisherige Rechnung 941cde2f8ec0), heute a9706524831a. Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>79e356dab0e6</t>
+          <t>eaa49d404283</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung bedbe4d72779 (bisherige Rechnung 8d6b015f6491), heute 79e356dab0e6. Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>c6108de5469a</t>
+          <t>85ab09092299</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 09a6b46168ef (bisherige Rechnung 2e35d889d037), heute c6108de5469a. Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>f420773e997c</t>
+          <t>b6ad9163b59b</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 80bcfa6fa500 (bisherige Rechnung 1f3bb870b0de), heute f420773e997c. Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>

--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/hygiene/Betriebsklar-Nachpruefliste-Lebensmittelhygiene.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/hygiene/Betriebsklar-Nachpruefliste-Lebensmittelhygiene.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="So geht's" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nachprüfliste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unterschrift" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,9 +33,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,10 +83,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,14 +467,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bitte prüfen und bestätigen. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Ihre Unterschrift braucht:</t>
+          <t>Bitte prüfen Sie die Positionen und bestätigen Sie sie per E-Mail. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Bestätigung braucht:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Unterschrift fehlt: Sie haben die Fassung freigegeben, uns liegt aber kein unterschriebenes Blatt vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
+          <t>• Bestätigung fehlt: Sie haben die Fassung freigegeben, uns liegt aber keine schriftliche Bestätigung vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
         </is>
       </c>
     </row>
@@ -496,7 +488,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
+          <t>• Vorlage: ohne schriftliche Bestätigung und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +512,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
+          <t>Bestätigen Sie bitte per E-Mail – eine Unterschrift ist nicht nötig. Es genügt eine kurze Antwort mit den Nummern der bestätigten Positionen, oder Sie schicken diese Datei mit ausgefüllter Spalte „Entscheidung“ mit Ihrer Antwort zurück. Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -535,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -596,291 +588,39 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Vorlage</t>
+          <t>Nennung im Vermerk</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>haccp</t>
+          <t>alle</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>58d605e11929</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Eigenkontrollen (HACCP)</t>
+          <t>Rolle statt Name</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
+          <t>Die App nennt Personen nicht mehr. Bisher ohne Namen: „Inhalt fachlich geprüft (Stand …)“ (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Inhalt fachlich geprüft von einem Lebensmittelfachbeauftragten, die Folgen bei Verstoß von einem Rechtsanwalt, Stand ….“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen Sie per E-Mail, dass die Nennung der Rolle so in Ordnung ist.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>hygieneplan</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>95846129d507</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Hygieneplan (Fassung lebensmittel)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>allergene</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>eaa49d404283</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Allergenliste</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ifsg_belehrung</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>85ab09092299</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Belehrung durch den Arbeitgeber (§ 43 IfSG)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>hygieneschulung</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>b6ad9163b59b</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Schulungsnachweis Lebensmittelhygiene (§ 4 LMHV)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Prüfvermerk zur Nachkontrolle ohne Unterschrift (Unterschriftszeile leer)). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Nennung im Vermerk</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>alle</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Rolle statt Name</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Die App nennt Personen nicht mehr. Bisher ohne Namen: „Inhalt fachlich geprüft (Stand …)“ (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Inhalt fachlich geprüft von einem Lebensmittelfachbeauftragten, die Folgen bei Verstoß von einem Rechtsanwalt, Stand ….“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen, dass die Nennung der Rolle so in Ordnung ist.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,ändern (Anmerkung),nicht mein Bereich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bestätigung der Nachprüfung – Lebensmittelfachbeauftragter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Ich habe die Positionen der Nachprüfliste vom 25.10.2026, die ich in der Spalte „Entscheidung“ mit „bestätigt“ markiert habe, in der jeweils genannten Fassung (Version bzw. Prüfsumme) fachlich geprüft bzw. durchgesehen. Sie sind nach meiner Prüfung zum genannten Stand zutreffend. Positionen mit „ändern“ oder „nicht mein Bereich“ sind nicht umfasst; für sie darf kein Vermerk angezeigt werden. Ändert sich ein Eintrag (neue Version) oder eine Vorlage (andere Prüfsumme), gilt diese Bestätigung dafür nicht mehr. Die Prüfung betrifft die allgemeinen Inhalte, nicht ihre Anwendung im Einzelfall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Anzeige in der App (nur bei bestätigten Positionen, ohne Namen, mit der Rolle): „Inhalt fachlich geprüft von einem Lebensmittelfachbeauftragten, die Folgen bei Verstoß von einem Rechtsanwalt, Stand ….“</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Stand der Prüfung:</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ort, Datum:</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Unterschrift:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(Lebensmittelfachbeauftragter)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>